--- a/template/하자보수현황_템플릿.xlsx
+++ b/template/하자보수현황_템플릿.xlsx
@@ -73,7 +73,6 @@
     <definedName name="ㅔ">#REF!</definedName>
     <definedName name="ㅠ">#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'하자현황'!$2:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'하자현황'!$A$1:$N$12</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,7 +81,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -117,6 +116,13 @@
       <color theme="1"/>
       <sz val="28"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <color theme="1"/>
+      <sz val="13"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -127,7 +133,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.0499893185216834"/>
+        <fgColor theme="3" tint="0.8999908444471572"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -164,7 +170,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -172,36 +178,33 @@
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -275,7 +278,7 @@
     <dxf>
       <border>
         <horizontal style="thin">
-          <color theme="0" tint="-0.1499069185460982"/>
+          <color theme="0" tint="-0.1498764000366222"/>
         </horizontal>
       </border>
     </dxf>
@@ -682,34 +685,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="10.06640625" defaultRowHeight="19.75"/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.06640625" defaultRowHeight="85.3" customHeight="1"/>
   <cols>
-    <col width="12.19921875" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
-    <col width="12.59765625" customWidth="1" style="3" min="2" max="2"/>
-    <col width="11.33203125" bestFit="1" customWidth="1" style="10" min="3" max="3"/>
-    <col width="9.19921875" bestFit="1" customWidth="1" style="3" min="4" max="4"/>
-    <col width="10.46484375" bestFit="1" customWidth="1" style="3" min="5" max="5"/>
-    <col width="54" customWidth="1" style="3" min="6" max="6"/>
-    <col width="21.06640625" customWidth="1" style="3" min="7" max="7"/>
-    <col width="11.796875" customWidth="1" style="3" min="8" max="8"/>
-    <col width="21.06640625" customWidth="1" style="3" min="9" max="9"/>
-    <col width="10.33203125" customWidth="1" style="3" min="10" max="10"/>
-    <col width="15.59765625" bestFit="1" customWidth="1" style="3" min="11" max="11"/>
-    <col width="16.06640625" customWidth="1" style="3" min="12" max="13"/>
-    <col width="14.33203125" customWidth="1" style="3" min="14" max="14"/>
-    <col width="10.06640625" customWidth="1" style="3" min="16" max="17"/>
-    <col width="10.06640625" customWidth="1" style="3" min="18" max="16384"/>
+    <col width="12.19921875" bestFit="1" customWidth="1" style="6" min="1" max="1"/>
+    <col width="12.59765625" customWidth="1" style="7" min="2" max="2"/>
+    <col width="11.33203125" bestFit="1" customWidth="1" style="7" min="3" max="3"/>
+    <col width="9.19921875" bestFit="1" customWidth="1" style="7" min="4" max="4"/>
+    <col width="10.46484375" bestFit="1" customWidth="1" style="8" min="5" max="5"/>
+    <col width="54" customWidth="1" style="9" min="6" max="6"/>
+    <col width="21.06640625" customWidth="1" style="5" min="7" max="7"/>
+    <col width="11.796875" customWidth="1" style="6" min="8" max="8"/>
+    <col width="21.06640625" customWidth="1" style="5" min="9" max="9"/>
+    <col width="10.33203125" customWidth="1" style="7" min="10" max="10"/>
+    <col width="15.59765625" bestFit="1" customWidth="1" style="10" min="11" max="11"/>
+    <col width="16.06640625" customWidth="1" style="10" min="12" max="12"/>
+    <col width="16.06640625" customWidth="1" style="7" min="13" max="13"/>
+    <col width="15.59765625" customWidth="1" style="8" min="14" max="14"/>
+    <col width="10.06640625" customWidth="1" style="4" min="15" max="15"/>
+    <col width="10.06640625" customWidth="1" style="5" min="16" max="18"/>
+    <col width="10.06640625" customWidth="1" style="5" min="19" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="60" customFormat="1" customHeight="1" s="2">
+    <row r="1" ht="60" customFormat="1" customHeight="1" s="3">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>터널 하자보수현황</t>
         </is>
       </c>
       <c r="B1" s="1" t="n"/>
-      <c r="C1" s="11" t="n"/>
+      <c r="C1" s="2" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
@@ -722,240 +727,185 @@
       <c r="M1" s="1" t="n"/>
       <c r="N1" s="1" t="n"/>
     </row>
-    <row r="2" ht="40.2" customHeight="1" s="13">
-      <c r="A2" s="12" t="inlineStr">
+    <row r="2" ht="40.2" customHeight="1" s="12">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>터널명</t>
         </is>
       </c>
-      <c r="C2" s="12" t="inlineStr">
+      <c r="C2" s="11" t="inlineStr">
         <is>
           <t>관리</t>
         </is>
       </c>
-      <c r="D2" s="12" t="inlineStr">
+      <c r="D2" s="11" t="inlineStr">
         <is>
           <t>공종</t>
         </is>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>위치</t>
         </is>
       </c>
-      <c r="F2" s="12" t="inlineStr">
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>하자내용</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>하자사진</t>
         </is>
       </c>
-      <c r="H2" s="12" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>조치일</t>
         </is>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>조치사진</t>
         </is>
       </c>
-      <c r="J2" s="12" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>조치여부</t>
         </is>
       </c>
-      <c r="K2" s="12" t="inlineStr">
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>업체명</t>
         </is>
       </c>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>담당자</t>
         </is>
       </c>
-      <c r="M2" s="12" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>전화번호</t>
         </is>
       </c>
-      <c r="N2" s="12" t="inlineStr">
+      <c r="N2" s="11" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="85.2" customHeight="1" s="13">
-      <c r="A3" s="8" t="n"/>
-      <c r="B3" s="4" t="n"/>
-      <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="6" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="8" t="n"/>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="9" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="85.2" customHeight="1" s="13">
-      <c r="A4" s="8" t="n"/>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="8" t="n"/>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="5" t="n"/>
-    </row>
-    <row r="5" ht="85.2" customHeight="1" s="13">
-      <c r="A5" s="8" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="8" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="85.2" customHeight="1" s="13">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="85.2" customHeight="1" s="13">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="85.2" customHeight="1" s="13">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="7" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="85.2" customHeight="1" s="13">
-      <c r="A9" s="8" t="n"/>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="85.2" customHeight="1" s="13">
-      <c r="A10" s="8" t="n"/>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="85.2" customHeight="1" s="13">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="85.2" customHeight="1" s="13">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="5" t="n"/>
-    </row>
+    <row r="3" ht="85.2" customHeight="1" s="12"/>
+    <row r="14" ht="85.2" customHeight="1" s="12"/>
+    <row r="15" ht="85.2" customHeight="1" s="12"/>
+    <row r="16" ht="85.2" customHeight="1" s="12"/>
+    <row r="17" ht="85.2" customHeight="1" s="12"/>
+    <row r="18" ht="85.2" customHeight="1" s="12"/>
+    <row r="19" ht="85.2" customHeight="1" s="12"/>
+    <row r="20" ht="85.2" customHeight="1" s="12"/>
+    <row r="21" ht="85.2" customHeight="1" s="12"/>
+    <row r="22" ht="85.2" customHeight="1" s="12"/>
+    <row r="23" ht="85.2" customHeight="1" s="12"/>
+    <row r="24" ht="85.2" customHeight="1" s="12"/>
+    <row r="25" ht="85.2" customHeight="1" s="12"/>
+    <row r="26" ht="85.2" customHeight="1" s="12"/>
+    <row r="27" ht="85.2" customHeight="1" s="12"/>
+    <row r="28" ht="85.2" customHeight="1" s="12"/>
+    <row r="29" ht="85.2" customHeight="1" s="12"/>
+    <row r="30" ht="85.2" customHeight="1" s="12"/>
+    <row r="31" ht="85.2" customHeight="1" s="12"/>
+    <row r="32" ht="85.2" customHeight="1" s="12"/>
+    <row r="33" ht="85.2" customHeight="1" s="12"/>
+    <row r="34" ht="85.2" customHeight="1" s="12"/>
+    <row r="35" ht="85.2" customHeight="1" s="12"/>
+    <row r="36" ht="85.2" customHeight="1" s="12"/>
+    <row r="37" ht="85.2" customHeight="1" s="12"/>
+    <row r="38" ht="85.2" customHeight="1" s="12"/>
+    <row r="39" ht="85.2" customHeight="1" s="12"/>
+    <row r="40" ht="85.2" customHeight="1" s="12"/>
+    <row r="41" ht="85.2" customHeight="1" s="12"/>
+    <row r="42" ht="85.2" customHeight="1" s="12"/>
+    <row r="43" ht="85.2" customHeight="1" s="12"/>
+    <row r="44" ht="85.2" customHeight="1" s="12"/>
+    <row r="45" ht="85.2" customHeight="1" s="12"/>
+    <row r="46" ht="85.2" customHeight="1" s="12"/>
+    <row r="47" ht="85.2" customHeight="1" s="12"/>
+    <row r="48" ht="85.2" customHeight="1" s="12"/>
+    <row r="49" ht="85.2" customHeight="1" s="12"/>
+    <row r="50" ht="85.2" customHeight="1" s="12"/>
+    <row r="51" ht="85.2" customHeight="1" s="12"/>
+    <row r="52" ht="85.2" customHeight="1" s="12"/>
+    <row r="53" ht="85.2" customHeight="1" s="12"/>
+    <row r="54" ht="85.2" customHeight="1" s="12"/>
+    <row r="55" ht="85.2" customHeight="1" s="12"/>
+    <row r="56" ht="85.2" customHeight="1" s="12"/>
+    <row r="57" ht="85.2" customHeight="1" s="12"/>
+    <row r="58" ht="85.2" customHeight="1" s="12"/>
+    <row r="59" ht="85.2" customHeight="1" s="12"/>
+    <row r="60" ht="85.2" customHeight="1" s="12"/>
+    <row r="61" ht="85.2" customHeight="1" s="12"/>
+    <row r="62" ht="85.2" customHeight="1" s="12"/>
+    <row r="63" ht="85.2" customHeight="1" s="12"/>
+    <row r="64" ht="85.2" customHeight="1" s="12"/>
+    <row r="65" ht="85.2" customHeight="1" s="12"/>
+    <row r="66" ht="85.2" customHeight="1" s="12"/>
+    <row r="67" ht="85.2" customHeight="1" s="12"/>
+    <row r="68" ht="85.2" customHeight="1" s="12"/>
+    <row r="69" ht="85.2" customHeight="1" s="12"/>
+    <row r="70" ht="85.2" customHeight="1" s="12"/>
+    <row r="71" ht="85.2" customHeight="1" s="12"/>
+    <row r="72" ht="85.2" customHeight="1" s="12"/>
+    <row r="73" ht="85.2" customHeight="1" s="12"/>
+    <row r="74" ht="85.2" customHeight="1" s="12"/>
+    <row r="75" ht="85.2" customHeight="1" s="12"/>
+    <row r="76" ht="85.2" customHeight="1" s="12"/>
+    <row r="77" ht="85.2" customHeight="1" s="12"/>
+    <row r="78" ht="85.2" customHeight="1" s="12"/>
+    <row r="79" ht="85.2" customHeight="1" s="12"/>
+    <row r="80" ht="85.2" customHeight="1" s="12"/>
+    <row r="81" ht="85.2" customHeight="1" s="12"/>
+    <row r="82" ht="85.2" customHeight="1" s="12"/>
+    <row r="83" ht="85.2" customHeight="1" s="12"/>
+    <row r="84" ht="85.2" customHeight="1" s="12"/>
+    <row r="85" ht="85.2" customHeight="1" s="12"/>
+    <row r="86" ht="85.2" customHeight="1" s="12"/>
+    <row r="87" ht="85.2" customHeight="1" s="12"/>
+    <row r="88" ht="85.2" customHeight="1" s="12"/>
+    <row r="89" ht="85.2" customHeight="1" s="12"/>
+    <row r="90" ht="85.2" customHeight="1" s="12"/>
+    <row r="91" ht="85.2" customHeight="1" s="12"/>
+    <row r="92" ht="85.2" customHeight="1" s="12"/>
+    <row r="93" ht="85.2" customHeight="1" s="12"/>
+    <row r="94" ht="85.2" customHeight="1" s="12"/>
+    <row r="95" ht="85.2" customHeight="1" s="12"/>
+    <row r="96" ht="85.2" customHeight="1" s="12"/>
+    <row r="97" ht="85.2" customHeight="1" s="12"/>
+    <row r="98" ht="85.2" customHeight="1" s="12"/>
+    <row r="99" ht="85.2" customHeight="1" s="12"/>
+    <row r="100" ht="85.2" customHeight="1" s="12"/>
+    <row r="101" ht="85.2" customHeight="1" s="12"/>
+    <row r="102" ht="85.2" customHeight="1" s="12"/>
+    <row r="103" ht="85.2" customHeight="1" s="12"/>
+    <row r="104" ht="85.2" customHeight="1" s="12"/>
+    <row r="105" ht="85.2" customHeight="1" s="12"/>
+    <row r="106" ht="85.2" customHeight="1" s="12"/>
+    <row r="107" ht="85.2" customHeight="1" s="12"/>
+    <row r="108" ht="85.2" customHeight="1" s="12"/>
+    <row r="109" ht="85.2" customHeight="1" s="12"/>
+    <row r="110" ht="85.2" customHeight="1" s="12"/>
+    <row r="111" ht="85.2" customHeight="1" s="12"/>
+    <row r="112" ht="85.2" customHeight="1" s="12"/>
+    <row r="113" ht="85.2" customHeight="1" s="12"/>
+    <row r="114" ht="85.2" customHeight="1" s="12"/>
+    <row r="115" ht="85.2" customHeight="1" s="12"/>
+    <row r="116" ht="85.2" customHeight="1" s="12"/>
+    <row r="117" ht="85.2" customHeight="1" s="12"/>
   </sheetData>
-  <conditionalFormatting sqref="J3:J12">
+  <conditionalFormatting sqref="J3:J1048576">
     <cfRule type="expression" priority="3" dxfId="0">
       <formula>$J3="완료"</formula>
     </cfRule>
